--- a/d.xlsx
+++ b/d.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10609"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EC39D054-2C28-4614-B67C-9BC3EEFE956A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C75CD19-ECA1-1D41-A79B-B61D3EAE2635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="27940" yWindow="11320" windowWidth="23260" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Simple Invoice" sheetId="1" r:id="rId1"/>
@@ -38,15 +38,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
   <si>
     <t>[Store Name]</t>
   </si>
   <si>
     <t>INVOICE</t>
-  </si>
-  <si>
-    <t>Your Company Slogan</t>
   </si>
   <si>
     <t>Street Address</t>
@@ -105,11 +102,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="3">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
-    <numFmt numFmtId="165" formatCode="[&lt;=9999999]###\-####;\(###\)\ ###\-####"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
+    <numFmt numFmtId="166" formatCode="[&lt;=9999999]###\-####;\(###\)\ ###\-####"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Arial"/>
@@ -245,10 +242,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
@@ -263,13 +260,13 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyProtection="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0">
@@ -295,22 +292,22 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="4"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="10" applyFont="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="11" applyFont="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="11" applyFont="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="9">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="9">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="13" applyFont="1">
@@ -325,16 +322,16 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="12" applyFont="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="8" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="8">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -990,16 +987,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:D28"/>
-  <sheetFormatPr defaultRowHeight="30" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.625" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="48.5" customWidth="1"/>
-    <col min="3" max="3" width="10.625" customWidth="1"/>
-    <col min="4" max="4" width="17.75" customWidth="1"/>
-    <col min="5" max="5" width="2.625" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" customWidth="1"/>
+    <col min="5" max="5" width="2.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="34.5" customHeight="1">
+    <row r="1" spans="2:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1008,155 +1005,155 @@
       </c>
       <c r="D1" s="17"/>
     </row>
-    <row r="2" spans="2:4" ht="30" customHeight="1">
+    <row r="2" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="2:4" ht="30" customHeight="1">
-      <c r="B3" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>4</v>
       </c>
       <c r="D3" s="6">
         <f ca="1">TODAY()</f>
         <v>45477</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="15" customHeight="1">
+    <row r="4" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>5</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>6</v>
       </c>
       <c r="D4" s="7">
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="30" customHeight="1">
+    <row r="5" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="D5" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="15" t="s">
+    </row>
+    <row r="6" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B6" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="30" customHeight="1">
-      <c r="B6" s="5" t="s">
+    <row r="7" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="15" customHeight="1">
-      <c r="B7" t="s">
+    <row r="8" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="15" customHeight="1">
-      <c r="B8" t="s">
+    <row r="9" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B11" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="15" customHeight="1">
-      <c r="B9" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" ht="15" customHeight="1">
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" ht="30" customHeight="1">
-      <c r="B11" s="8" t="s">
+    <row r="12" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B12" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="12" spans="2:4" ht="30" customHeight="1">
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" ht="30" customHeight="1">
+    </row>
+    <row r="13" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
       <c r="D13" s="9"/>
     </row>
-    <row r="14" spans="2:4" ht="30" customHeight="1">
+    <row r="14" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
       <c r="D14" s="9"/>
     </row>
-    <row r="15" spans="2:4" ht="30" customHeight="1">
+    <row r="15" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
       <c r="D15" s="9"/>
     </row>
-    <row r="16" spans="2:4" ht="30" customHeight="1">
+    <row r="16" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
       <c r="D16" s="9"/>
     </row>
-    <row r="17" spans="2:4" ht="30" customHeight="1">
+    <row r="17" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
       <c r="D17" s="9"/>
     </row>
-    <row r="18" spans="2:4" ht="30" customHeight="1">
+    <row r="18" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
       <c r="D18" s="9"/>
     </row>
-    <row r="19" spans="2:4" ht="30" customHeight="1">
+    <row r="19" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
       <c r="D19" s="9"/>
     </row>
-    <row r="20" spans="2:4" ht="30" customHeight="1">
+    <row r="20" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
       <c r="D20" s="9"/>
     </row>
-    <row r="21" spans="2:4" ht="30" customHeight="1">
+    <row r="21" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
       <c r="D21" s="9"/>
     </row>
-    <row r="22" spans="2:4" ht="30" customHeight="1">
+    <row r="22" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
       <c r="D22" s="9"/>
     </row>
-    <row r="23" spans="2:4" ht="30" customHeight="1">
+    <row r="23" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
       <c r="D23" s="9"/>
     </row>
-    <row r="24" spans="2:4" ht="30" customHeight="1">
+    <row r="24" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C24" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D24" s="11">
         <f>SUBTOTAL(109,Invoice[AMOUNT])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:4" ht="5.45" customHeight="1">
+    <row r="25" spans="2:4" ht="5.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C25" s="10"/>
       <c r="D25" s="16"/>
     </row>
-    <row r="26" spans="2:4" ht="30" customHeight="1">
+    <row r="26" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="18" t="str">
         <f>"Make all checks payable to "&amp;Company_Name&amp;""</f>
         <v>Make all checks payable to [Store Name]</v>
@@ -1164,16 +1161,16 @@
       <c r="C26" s="18"/>
       <c r="D26" s="18"/>
     </row>
-    <row r="27" spans="2:4" ht="30" customHeight="1">
+    <row r="27" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C27" s="18"/>
       <c r="D27" s="18"/>
     </row>
-    <row r="28" spans="2:4" ht="30" customHeight="1">
+    <row r="28" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C28" s="19"/>
       <c r="D28" s="19"/>
@@ -1225,35 +1222,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="26" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac37c1753acd5e330d2062ccec26ea66">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3b340c7101c92c5120abd06486f94548" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -1553,14 +1521,72 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54BA574B-D25A-47D2-A157-4CAA56EBF4AE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FFA2500-0DAB-4D00-A350-6145D1830994}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E84B1AD-03C0-4B52-BD7A-D11E11AAE50D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54BA574B-D25A-47D2-A157-4CAA56EBF4AE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FFA2500-0DAB-4D00-A350-6145D1830994}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E84B1AD-03C0-4B52-BD7A-D11E11AAE50D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>